--- a/datos-referencia/mermas.xlsx
+++ b/datos-referencia/mermas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,13 +434,116 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>motivo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>coste_unitario</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>coste_merma</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lubina fresca</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Caducidad</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chocolate 70%</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rotura</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Entrecot</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.4</v>
       </c>
     </row>
   </sheetData>

--- a/datos-referencia/mermas.xlsx
+++ b/datos-referencia/mermas.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mermas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,30 +424,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>producto</t>
+          <t>ingrediente</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>cantidad</t>
+          <t>cantidad_merma</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>unidad</t>
+          <t>causa</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>coste_unitario</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>coste_merma</t>
         </is>
@@ -456,32 +446,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lubina fresca</t>
+          <t>Harina</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Caducidad</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45</v>
+          <t>Rotura</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
@@ -492,27 +474,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chocolate 70%</t>
+          <t>Tomate</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>Rotura</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.6</v>
+      <c r="E3" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -523,27 +497,134 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Entrecot</t>
+          <t>Aceite oliva</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+          <t>Error preparación</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Temperatura</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>22</v>
-      </c>
-      <c r="G4" t="n">
-        <v>26.4</v>
+      <c r="E5" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mantequilla</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rotura</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lubina fresca</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Error preparación</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sal marina</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>

--- a/datos-referencia/mermas.xlsx
+++ b/datos-referencia/mermas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,30 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>cantidad_merma</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>causa</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>coste_unitario</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>coste_merma</t>
         </is>
@@ -446,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -454,177 +469,353 @@
           <t>Harina</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Rotura</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.8</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cereales</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Contaminación</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tomate</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>Pan brioche</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Panaderia</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Rotura</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>4.5</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Temperatura</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aceite oliva</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Error preparación</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>18.4</v>
+          <t>Mantequilla</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Caducidad</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pollo</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Temperatura</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2.6</v>
+          <t>Huevo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Contaminación</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mantequilla</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Rotura</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>16.2</v>
+          <t>Arroz bomba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cereales</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Error preparación</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lubina fresca</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>Pan brioche</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Panaderia</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Temperatura</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>36</v>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pollo</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Error preparación</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>13.65</v>
+          <t>Pan brioche</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Panaderia</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Caducidad</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sal marina</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+          <t>Aceite oliva</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aceites</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Error preparación</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aceite oliva</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Aceites</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Contaminación</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Queso</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>0.4</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Temperatura</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.48</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rotura</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>

--- a/datos-referencia/mermas.xlsx
+++ b/datos-referencia/mermas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>fecha</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>causa</t>
-  </si>
-  <si>
-    <t>coste_unitario</t>
   </si>
   <si>
     <t>coste_merma</t>
@@ -395,10 +392,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,9 +416,6 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
